--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -912,189 +912,189 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
@@ -1108,798 +1108,798 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10000.0_3000_F.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10000.0_3000_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -895,994 +895,994 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>10000.0_3000_F.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10000.0_3000_F.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,6 +868,23 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>870 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Marcos F.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15,0 km</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11 m</t>
         </is>
       </c>
     </row>
@@ -882,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A143"/>
+  <dimension ref="A1:A144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,994 +912,1001 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>15000.0_4200_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>10000.0_3000_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10000.0_3000_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4000.6_1659_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -895,1001 +895,1001 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>15000.0_4200_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10000.0_3000_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15000.0_4200_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>10000.0_3000_F.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -895,7 +895,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
@@ -909,273 +909,273 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
@@ -1189,112 +1189,112 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
@@ -1308,231 +1308,231 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
@@ -1546,336 +1546,336 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>357,8 km</t>
+          <t>360,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.989 m</t>
+          <t>5.000 m</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A142"/>
+  <dimension ref="A1:A143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,987 +895,994 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>3000.0_930_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>7061.6_2110_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>364,8 km</t>
+          <t>372,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.993 m</t>
+          <t>5.001 m</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A143"/>
+  <dimension ref="A1:A144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,623 +895,623 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>7000.0_2310_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7000.0_2310_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
@@ -1525,364 +1525,371 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>8000.0_2758_F.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>6023.1_2321_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>357,8 km</t>
+          <t>383,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.989 m</t>
+          <t>5.537 m</t>
         </is>
       </c>
     </row>
@@ -868,6 +868,74 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>870 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Erivando F.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12,0 km</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>109 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ismael Q.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5,5 km</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>51 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flavio B.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5,5 km</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>45 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Eduarda L.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5,2 km</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>51 m</t>
         </is>
       </c>
     </row>
@@ -882,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A142"/>
+  <dimension ref="A1:A148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,98 +963,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
@@ -1000,882 +1068,924 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>7511.5_2322_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4077.1_1454_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7061.6_2110_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4777.4_1215_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>10533.4_4020_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2014.2_647_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -891,7 +891,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Flavio B.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -901,14 +901,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51 m</t>
+          <t>45 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Flavio B.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45 m</t>
+          <t>51 m</t>
         </is>
       </c>
     </row>
@@ -963,210 +963,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
@@ -1180,812 +1180,812 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>458,7 km</t>
+          <t>464,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.613 m</t>
+          <t>5.669 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>350,8 km</t>
+          <t>360,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.805 m</t>
+          <t>4.930 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>209,5 km</t>
+          <t>215,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.538 m</t>
+          <t>2.583 m</t>
         </is>
       </c>
     </row>
@@ -551,34 +551,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>176,4 km</t>
+          <t>180,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.497 m</t>
+          <t>1.471 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>175,3 km</t>
+          <t>176,4 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.422 m</t>
+          <t>1.497 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>168,6 km</t>
+          <t>173,1 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.332 m</t>
+          <t>1.384 m</t>
         </is>
       </c>
     </row>
@@ -868,6 +868,23 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>870 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fabio O.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>42,8 km</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>585 m</t>
         </is>
       </c>
     </row>
@@ -882,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A148"/>
+  <dimension ref="A1:A159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,49 +912,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
@@ -951,700 +968,700 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
@@ -1658,42 +1675,42 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
@@ -1707,217 +1724,294 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>6012.6_2984_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6023.1_2082_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>3019.8_1453_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4077.1_1454_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>47036.4_21887_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5053.8_1563_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4992.7_1755_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>5537.2_1928_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>5014.3_1731_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>3014.7_822_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7012.1_3931_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>464,8 km</t>
+          <t>473,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.669 m</t>
+          <t>5.764 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>383,8 km</t>
+          <t>391,2 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.537 m</t>
+          <t>5.616 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>360,8 km</t>
+          <t>376,3 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.930 m</t>
+          <t>5.096 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>263,0 km</t>
+          <t>275,0 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.822 m</t>
+          <t>2.914 m</t>
         </is>
       </c>
     </row>
@@ -522,63 +522,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>215,0 km</t>
+          <t>223,5 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.583 m</t>
+          <t>2.686 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>189,9 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.636 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>180,3 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.471 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>176,4 km</t>
+          <t>180,3 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.497 m</t>
+          <t>1.471 m</t>
         </is>
       </c>
     </row>
@@ -636,34 +636,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>142,2 km</t>
+          <t>147,7 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.084 m</t>
+          <t>1.891 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>138,7 km</t>
+          <t>147,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.781 m</t>
+          <t>1.136 m</t>
         </is>
       </c>
     </row>
@@ -687,34 +687,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>124,9 km</t>
+          <t>129,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.737 m</t>
+          <t>882 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>124,0 km</t>
+          <t>124,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>855 m</t>
+          <t>1.737 m</t>
         </is>
       </c>
     </row>
@@ -738,34 +738,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>107,7 km</t>
+          <t>113,9 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>804 m</t>
+          <t>782 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>105,9 km</t>
+          <t>111,9 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>782 m</t>
+          <t>893 m</t>
         </is>
       </c>
     </row>
@@ -823,34 +823,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bruninho W.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>70,5 km</t>
+          <t>71,5 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>646 m</t>
+          <t>505 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Bruninho W.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>66,5 km</t>
+          <t>70,5 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>475 m</t>
+          <t>646 m</t>
         </is>
       </c>
     </row>
@@ -885,6 +885,23 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>585 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>José Welligton Dos Santos W.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>36,3 km</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>503 m</t>
         </is>
       </c>
     </row>
@@ -899,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A159"/>
+  <dimension ref="A1:A178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,518 +929,518 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
@@ -1437,581 +1454,714 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5008.8_1593_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>9027.2_3128_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>5024.1_1795_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>8120.9_2737_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4933.2_1199_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>5021.4_2461_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>5017.9_2549_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>5014.8_2009_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4073.8_1409_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>8506.9_2757_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4078.1_1810_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>12326.4_4833_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>12004.8_4293_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4499.3_1358_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>3013.0_846_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>3005.2_1040_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6051.3_1877_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4613.1_1806_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10533.4_4020_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>473,8 km</t>
+          <t>476,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.764 m</t>
+          <t>5.790 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>223,5 km</t>
+          <t>230,1 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.686 m</t>
+          <t>2.775 m</t>
         </is>
       </c>
     </row>
@@ -551,102 +551,102 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>185,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.521 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>180,3 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.471 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>175,4 km</t>
+          <t>180,6 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.838 m</t>
+          <t>1.471 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>173,1 km</t>
+          <t>175,4 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.384 m</t>
+          <t>1.838 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>163,0 km</t>
+          <t>164,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.103 m</t>
+          <t>1.557 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>154,8 km</t>
+          <t>163,0 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.486 m</t>
+          <t>2.103 m</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>129,0 km</t>
+          <t>131,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>113,9 km</t>
+          <t>118,9 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>782 m</t>
+          <t>798 m</t>
         </is>
       </c>
     </row>
@@ -806,34 +806,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>87,6 km</t>
+          <t>88,7 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.037 m</t>
+          <t>1.118 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>84,4 km</t>
+          <t>87,6 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.050 m</t>
+          <t>1.037 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A179"/>
+  <dimension ref="A1:A188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,1246 +929,1309 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>17012.6_5869_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1734.2_553_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>3614.8_970_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>9507.9_2851_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>8529.2_2334_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>5012.7_1713_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4678.8_1840_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1002.0_533_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>5010.6_1464_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>476,8 km</t>
+          <t>532,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.790 m</t>
+          <t>6.208 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>391,3 km</t>
+          <t>447,4 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.617 m</t>
+          <t>6.042 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>275,0 km</t>
+          <t>297,0 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.914 m</t>
+          <t>3.449 m</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>72,7 km</t>
+          <t>78,0 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>742 m</t>
+          <t>561 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>71,5 km</t>
+          <t>72,7 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>505 m</t>
+          <t>742 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A188"/>
+  <dimension ref="A1:A192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,1001 +929,1001 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
@@ -1937,14 +1937,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
@@ -1958,280 +1958,308 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5024.6_1753_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4705.5_1241_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>5008.8_1593_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2060.0_802_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>532,6 km</t>
+          <t>542,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.208 m</t>
+          <t>6.218 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>447,4 km</t>
+          <t>467,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.042 m</t>
+          <t>6.339 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>376,4 km</t>
+          <t>394,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.096 m</t>
+          <t>5.301 m</t>
         </is>
       </c>
     </row>
@@ -522,29 +522,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230,1 km</t>
+          <t>251,1 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.775 m</t>
+          <t>2.953 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>189,9 km</t>
+          <t>194,7 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.636 m</t>
+          <t>1.602 m</t>
         </is>
       </c>
     </row>
@@ -556,63 +556,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>185,3 km</t>
+          <t>190,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.521 m</t>
+          <t>1.548 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>189,9 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.636 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>180,6 km</t>
+          <t>185,4 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.471 m</t>
+          <t>1.927 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>175,4 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.838 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
@@ -624,46 +624,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>164,8 km</t>
+          <t>174,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.557 m</t>
+          <t>1.675 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>163,0 km</t>
+          <t>169,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.103 m</t>
+          <t>971 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>147,8 km</t>
+          <t>163,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.891 m</t>
+          <t>2.103 m</t>
         </is>
       </c>
     </row>
@@ -675,114 +675,114 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>147,2 km</t>
+          <t>152,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.136 m</t>
+          <t>1.163 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>137,7 km</t>
+          <t>147,8 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>856 m</t>
+          <t>1.891 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>133,9 km</t>
+          <t>143,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.888 m</t>
+          <t>980 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>131,9 km</t>
+          <t>133,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>882 m</t>
+          <t>890 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>124,9 km</t>
+          <t>133,9 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.737 m</t>
+          <t>1.888 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>121,2 km</t>
+          <t>124,9 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.201 m</t>
+          <t>1.737 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>118,9 km</t>
+          <t>121,2 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>798 m</t>
+          <t>1.201 m</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>78,0 km</t>
+          <t>82,8 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>561 m</t>
+          <t>841 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>72,7 km</t>
+          <t>78,0 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>742 m</t>
+          <t>561 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A192"/>
+  <dimension ref="A1:A206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,161 +929,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
@@ -1097,532 +1097,532 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
@@ -1636,105 +1636,105 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
@@ -1748,518 +1748,616 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>22012.0_8790_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10058.8_3483_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2003.1_722_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>5021.9_1788_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2002.2_938_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10002.4_5136_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>5022.6_1526_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>21442.0_7959_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4702.3_1489_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2971.2_2253_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10174.3_3680_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>8187.1_2322_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>3013.0_846_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>542,7 km</t>
+          <t>557,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.218 m</t>
+          <t>6.397 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>394,5 km</t>
+          <t>400,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.301 m</t>
+          <t>5.383 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>194,7 km</t>
+          <t>203,1 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.602 m</t>
+          <t>1.643 m</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>152,2 km</t>
+          <t>162,3 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.163 m</t>
+          <t>1.245 m</t>
         </is>
       </c>
     </row>
@@ -692,19 +692,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>147,8 km</t>
+          <t>157,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.891 m</t>
+          <t>2.023 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -714,31 +714,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>980 m</t>
+          <t>2.011 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>133,9 km</t>
+          <t>143,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>890 m</t>
+          <t>980 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.888 m</t>
+          <t>890 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>88,7 km</t>
+          <t>96,7 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.118 m</t>
+          <t>1.204 m</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78,0 km</t>
+          <t>82,2 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>561 m</t>
+          <t>591 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A206"/>
+  <dimension ref="A1:A216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,1435 +929,1505 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2305.1_940_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>8028.3_3060_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>5014.3_1731_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>3005.2_1040_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>5079.1_1762_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1734.2_553_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>5013.4_1650_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>5014.8_1403_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1057.3_319_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>15016.9_6221_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>557,7 km</t>
+          <t>572,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.397 m</t>
+          <t>6.562 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>467,5 km</t>
+          <t>489,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.339 m</t>
+          <t>6.968 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>400,5 km</t>
+          <t>410,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.383 m</t>
+          <t>5.506 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>251,1 km</t>
+          <t>261,1 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.953 m</t>
+          <t>3.074 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>190,3 km</t>
+          <t>200,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.548 m</t>
+          <t>1.638 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>189,9 km</t>
+          <t>199,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.636 m</t>
+          <t>1.696 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>185,4 km</t>
+          <t>193,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.927 m</t>
+          <t>2.046 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>169,9 km</t>
+          <t>172,0 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>971 m</t>
+          <t>977 m</t>
         </is>
       </c>
     </row>
@@ -658,80 +658,80 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>163,0 km</t>
+          <t>169,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.103 m</t>
+          <t>2.174 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>162,3 km</t>
+          <t>164,0 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.245 m</t>
+          <t>2.116 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>157,5 km</t>
+          <t>162,3 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.023 m</t>
+          <t>1.245 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>143,9 km</t>
+          <t>150,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.011 m</t>
+          <t>1.062 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>143,9 km</t>
+          <t>149,7 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>980 m</t>
+          <t>2.082 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A216"/>
+  <dimension ref="A1:A229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,1505 +929,1596 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>7015.4_2141_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>5122.9_1812_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>5894.5_1785_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>21470.9_7911_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>7022.4_3008_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>22320.3_9183_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>12006.9_5463_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1027.7_364_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>6549.3_2336_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>9013.7_2337_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1114.9_359_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>18102.7_4949_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>15009.9_5893_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>572,7 km</t>
+          <t>577,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.562 m</t>
+          <t>6.613 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>489,8 km</t>
+          <t>510,9 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.968 m</t>
+          <t>7.229 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>410,5 km</t>
+          <t>422,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.506 m</t>
+          <t>5.642 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>261,1 km</t>
+          <t>271,1 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.074 m</t>
+          <t>3.189 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>203,1 km</t>
+          <t>207,0 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.643 m</t>
+          <t>1.717 m</t>
         </is>
       </c>
     </row>
@@ -670,34 +670,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>164,0 km</t>
+          <t>167,3 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.116 m</t>
+          <t>1.295 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>162,3 km</t>
+          <t>164,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.245 m</t>
+          <t>2.116 m</t>
         </is>
       </c>
     </row>
@@ -755,34 +755,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>124,9 km</t>
+          <t>127,2 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.737 m</t>
+          <t>1.277 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>121,2 km</t>
+          <t>124,9 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.201 m</t>
+          <t>1.737 m</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A229"/>
+  <dimension ref="A1:A238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,546 +929,546 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
@@ -1482,154 +1482,154 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
@@ -1643,882 +1643,945 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>13460.9_4967_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10042.8_3601_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>9013.7_2337_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>5601.8_2355_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>21202.9_7130_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>5017.3_1786_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>10022.1_2875_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2051.8_860_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -946,1757 +946,1757 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>577,8 km</t>
+          <t>593,1 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.613 m</t>
+          <t>6.848 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>511,0 km</t>
+          <t>532,1 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.229 m</t>
+          <t>7.535 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>422,8 km</t>
+          <t>432,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.642 m</t>
+          <t>5.820 m</t>
         </is>
       </c>
     </row>
@@ -568,51 +568,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>203,5 km</t>
+          <t>204,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.129 m</t>
+          <t>1.696 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200,3 km</t>
+          <t>203,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.638 m</t>
+          <t>2.129 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>199,0 km</t>
+          <t>200,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.696 m</t>
+          <t>1.638 m</t>
         </is>
       </c>
     </row>
@@ -653,24 +653,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>169,0 km</t>
+          <t>172,4 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>960 m</t>
+          <t>1.325 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -680,24 +680,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.174 m</t>
+          <t>960 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>167,4 km</t>
+          <t>169,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.295 m</t>
+          <t>2.174 m</t>
         </is>
       </c>
     </row>
@@ -721,34 +721,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150,9 km</t>
+          <t>159,6 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.062 m</t>
+          <t>2.201 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>149,6 km</t>
+          <t>157,9 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.082 m</t>
+          <t>1.117 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>134,0 km</t>
+          <t>140,0 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>890 m</t>
+          <t>942 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>127,2 km</t>
+          <t>132,2 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.277 m</t>
+          <t>1.334 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>96,8 km</t>
+          <t>103,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.204 m</t>
+          <t>1.284 m</t>
         </is>
       </c>
     </row>
@@ -908,15 +908,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Jandson P.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>66,7 km</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>917 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Pablo T.</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>59,2 km</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>870 m</t>
         </is>
@@ -933,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A252"/>
+  <dimension ref="A1:A269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,1435 +963,1435 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
@@ -2388,315 +2405,434 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>4763.8_1720_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>5024.6_1753_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4840.9_1332_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>7419.2_3469_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>6023.1_2321_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>12003.8_4287_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>6146.9_2154_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2175.4_712_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>8069.5_2626_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>10022.1_2875_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>8223.8_2382_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>10013.5_3516_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>4499.3_1358_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1884.9_866_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>5008.0_1650_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>8269.0_2920_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>593,1 km</t>
+          <t>596,1 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.848 m</t>
+          <t>6.879 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>532,1 km</t>
+          <t>537,4 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.535 m</t>
+          <t>7.595 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>422,4 km</t>
+          <t>428,3 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.623 m</t>
+          <t>3.684 m</t>
         </is>
       </c>
     </row>
@@ -556,63 +556,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>206,9 km</t>
+          <t>214,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.717 m</t>
+          <t>1.747 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>204,8 km</t>
+          <t>210,6 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.696 m</t>
+          <t>1.719 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>203,5 km</t>
+          <t>204,8 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.129 m</t>
+          <t>1.696 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200,3 km</t>
+          <t>203,5 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.638 m</t>
+          <t>2.129 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>181,5 km</t>
+          <t>187,1 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.714 m</t>
+          <t>1.782 m</t>
         </is>
       </c>
     </row>
@@ -653,34 +653,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>172,4 km</t>
+          <t>177,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.325 m</t>
+          <t>1.087 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>169,0 km</t>
+          <t>172,4 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>960 m</t>
+          <t>1.325 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>132,2 km</t>
+          <t>138,8 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.334 m</t>
+          <t>1.396 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>111,9 km</t>
+          <t>120,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>893 m</t>
+          <t>1.005 m</t>
         </is>
       </c>
     </row>
@@ -828,63 +828,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>103,8 km</t>
+          <t>114,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.284 m</t>
+          <t>1.390 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>87,6 km</t>
+          <t>92,8 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.037 m</t>
+          <t>936 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>82,8 km</t>
+          <t>89,7 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>841 m</t>
+          <t>653 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>82,2 km</t>
+          <t>87,6 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>591 m</t>
+          <t>1.037 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A269"/>
+  <dimension ref="A1:A283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,1876 +963,1974 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5219.5_2096_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>6137.8_2406_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>5027.8_1361_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>10174.3_3680_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1734.2_553_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>12003.8_4287_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>5119.6_3153_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>6549.3_2336_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>6022.4_2122_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>6472.0_2501_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>5026.3_1748_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>8104.2_2652_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>4763.8_1720_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>596,1 km</t>
+          <t>649,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.879 m</t>
+          <t>8.740 m</t>
         </is>
       </c>
     </row>
@@ -471,46 +471,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>537,4 km</t>
+          <t>592,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.595 m</t>
+          <t>9.495 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>432,8 km</t>
+          <t>439,1 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.820 m</t>
+          <t>3.775 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>428,3 km</t>
+          <t>432,8 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.684 m</t>
+          <t>5.820 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>297,0 km</t>
+          <t>321,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.449 m</t>
+          <t>3.679 m</t>
         </is>
       </c>
     </row>
@@ -636,51 +636,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>182,4 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.406 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>177,2 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.087 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>172,4 km</t>
+          <t>177,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.325 m</t>
+          <t>1.087 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A283"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,287 +963,287 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
@@ -1257,1372 +1257,1372 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
@@ -2636,301 +2636,343 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5025.8_1214_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>21106.2_7925_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>5021.9_1788_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>3716.0_1233_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>4073.8_1409_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>5007.0_1820_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>649,2 km</t>
+          <t>661,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.740 m</t>
+          <t>8.840 m</t>
         </is>
       </c>
     </row>
@@ -471,46 +471,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>592,8 km</t>
+          <t>602,7 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.495 m</t>
+          <t>9.596 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>439,1 km</t>
+          <t>450,9 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.775 m</t>
+          <t>6.013 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>432,8 km</t>
+          <t>449,0 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.820 m</t>
+          <t>3.846 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>271,1 km</t>
+          <t>279,4 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.189 m</t>
+          <t>3.318 m</t>
         </is>
       </c>
     </row>
@@ -556,46 +556,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>214,9 km</t>
+          <t>230,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.747 m</t>
+          <t>1.875 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>210,6 km</t>
+          <t>219,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.719 m</t>
+          <t>1.825 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>204,8 km</t>
+          <t>210,6 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.696 m</t>
+          <t>1.719 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>203,5 km</t>
+          <t>208,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.129 m</t>
+          <t>2.187 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>187,1 km</t>
+          <t>194,7 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.782 m</t>
+          <t>1.848 m</t>
         </is>
       </c>
     </row>
@@ -653,102 +653,102 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>182,1 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.104 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>177,2 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.087 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>169,0 km</t>
+          <t>172,6 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.174 m</t>
+          <t>2.373 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>164,0 km</t>
+          <t>171,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.116 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>159,6 km</t>
+          <t>169,0 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.201 m</t>
+          <t>2.174 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>157,9 km</t>
+          <t>164,0 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.117 m</t>
+          <t>2.116 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140,0 km</t>
+          <t>152,0 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>942 m</t>
+          <t>1.026 m</t>
         </is>
       </c>
     </row>
@@ -777,46 +777,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>138,8 km</t>
+          <t>143,6 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.396 m</t>
+          <t>1.454 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>124,9 km</t>
+          <t>125,1 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.737 m</t>
+          <t>1.063 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>120,1 km</t>
+          <t>124,9 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.005 m</t>
+          <t>1.737 m</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>92,8 km</t>
+          <t>94,2 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>936 m</t>
+          <t>711 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89,7 km</t>
+          <t>92,8 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>653 m</t>
+          <t>936 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A289"/>
+  <dimension ref="A1:A309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,1911 +963,1911 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
@@ -2881,98 +2881,238 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10105.5_3599_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>6009.3_2290_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>7098.4_4003_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4678.8_1840_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>48019.1_21921_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>6137.8_2406_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>16008.9_5968_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20105.6_7766_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>15010.1_5518_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>4763.8_1720_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>8529.2_2334_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>55771.9_25830_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>4943.8_1258_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>6051.3_1877_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>7061.6_2110_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1057.3_319_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>11004.9_3283_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4153.2_3559_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>8525.9_2945_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>661,2 km</t>
+          <t>662,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.840 m</t>
+          <t>8.842 m</t>
         </is>
       </c>
     </row>
@@ -471,46 +471,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>602,7 km</t>
+          <t>617,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.596 m</t>
+          <t>9.785 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>450,9 km</t>
+          <t>454,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.013 m</t>
+          <t>3.900 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>449,0 km</t>
+          <t>450,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.846 m</t>
+          <t>6.013 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>279,4 km</t>
+          <t>289,7 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.318 m</t>
+          <t>3.432 m</t>
         </is>
       </c>
     </row>
@@ -585,34 +585,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>210,6 km</t>
+          <t>219,4 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.719 m</t>
+          <t>2.320 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>208,3 km</t>
+          <t>215,6 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.187 m</t>
+          <t>1.758 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>182,4 km</t>
+          <t>192,5 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.406 m</t>
+          <t>1.491 m</t>
         </is>
       </c>
     </row>
@@ -687,51 +687,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>172,6 km</t>
+          <t>174,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.373 m</t>
+          <t>2.239 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>171,9 km</t>
+          <t>172,6 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.199 m</t>
+          <t>2.373 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>169,0 km</t>
+          <t>171,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.174 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>164,0 km</t>
+          <t>168,8 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.116 m</t>
+          <t>2.170 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>143,6 km</t>
+          <t>150,1 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.454 m</t>
+          <t>1.519 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A309"/>
+  <dimension ref="A1:A320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,259 +963,259 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
@@ -1229,1890 +1229,1967 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>55771.9_25830_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>6100.0_2246_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>7022.4_3008_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4078.1_1810_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>7012.1_3931_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>8187.1_2322_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>6023.1_2321_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>12003.8_4287_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>5888.2_1831_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>10027.3_2906_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>10002.4_5136_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>662,2 km</t>
+          <t>672,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.842 m</t>
+          <t>8.981 m</t>
         </is>
       </c>
     </row>
@@ -471,46 +471,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>617,8 km</t>
+          <t>627,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.785 m</t>
+          <t>9.908 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>454,8 km</t>
+          <t>467,4 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.900 m</t>
+          <t>6.241 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>450,9 km</t>
+          <t>461,8 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.013 m</t>
+          <t>3.956 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>321,0 km</t>
+          <t>333,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.679 m</t>
+          <t>3.745 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>289,7 km</t>
+          <t>296,3 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.432 m</t>
+          <t>3.514 m</t>
         </is>
       </c>
     </row>
@@ -556,46 +556,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230,9 km</t>
+          <t>237,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.875 m</t>
+          <t>1.905 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>219,8 km</t>
+          <t>226,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.825 m</t>
+          <t>2.402 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>219,4 km</t>
+          <t>219,8 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.320 m</t>
+          <t>1.825 m</t>
         </is>
       </c>
     </row>
@@ -653,34 +653,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>182,1 km</t>
+          <t>187,8 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.104 m</t>
+          <t>2.423 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>182,1 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.104 m</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>174,0 km</t>
+          <t>180,6 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.239 m</t>
+          <t>2.321 m</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>172,6 km</t>
+          <t>179,6 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.373 m</t>
+          <t>2.455 m</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>171,9 km</t>
+          <t>178,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -755,68 +755,68 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>152,0 km</t>
+          <t>157,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.026 m</t>
+          <t>1.601 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150,1 km</t>
+          <t>152,0 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.519 m</t>
+          <t>1.026 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>125,1 km</t>
+          <t>131,7 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.063 m</t>
+          <t>1.819 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>124,9 km</t>
+          <t>126,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.737 m</t>
+          <t>1.063 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>114,2 km</t>
+          <t>122,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.390 m</t>
+          <t>1.463 m</t>
         </is>
       </c>
     </row>
@@ -891,34 +891,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bruninho W.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>70,5 km</t>
+          <t>73,3 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>646 m</t>
+          <t>995 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Bruninho W.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>66,7 km</t>
+          <t>70,5 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>917 m</t>
+          <t>646 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A320"/>
+  <dimension ref="A1:A339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,2233 +963,2366 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>7511.5_2322_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>21306.6_7154_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>12008.4_3832_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>21017.3_7815_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>5010.6_1464_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>5007.5_3389_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>469.2_158_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>5537.2_1928_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2003.1_722_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>11006.2_3422_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>6609.8_2216_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>419.0_180_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>8200.0_2760_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>7008.0_2227_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>6022.4_2122_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>5760.0_2094_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>4943.8_1258_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>4759.9_1521_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2305.1_940_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>672,6 km</t>
+          <t>684,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.981 m</t>
+          <t>9.121 m</t>
         </is>
       </c>
     </row>
@@ -471,46 +471,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>627,8 km</t>
+          <t>643,0 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.908 m</t>
+          <t>10.084 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>474,4 km</t>
+          <t>481,7 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.064 m</t>
+          <t>6.411 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>467,4 km</t>
+          <t>474,4 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.241 m</t>
+          <t>4.064 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>237,3 km</t>
+          <t>243,1 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.905 m</t>
+          <t>1.946 m</t>
         </is>
       </c>
     </row>
@@ -619,34 +619,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>194,7 km</t>
+          <t>202,5 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.848 m</t>
+          <t>1.572 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>192,5 km</t>
+          <t>194,7 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.491 m</t>
+          <t>1.848 m</t>
         </is>
       </c>
     </row>
@@ -658,63 +658,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>187,8 km</t>
+          <t>192,8 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.423 m</t>
+          <t>2.481 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>182,1 km</t>
+          <t>191,6 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.104 m</t>
+          <t>2.761 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>180,6 km</t>
+          <t>184,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.321 m</t>
+          <t>2.510 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>179,6 km</t>
+          <t>182,1 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.455 m</t>
+          <t>1.104 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>168,8 km</t>
+          <t>173,7 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.170 m</t>
+          <t>2.226 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>157,1 km</t>
+          <t>168,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.601 m</t>
+          <t>2.045 m</t>
         </is>
       </c>
     </row>
@@ -794,63 +794,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140,5 km</t>
+          <t>150,5 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.930 m</t>
+          <t>2.028 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>131,7 km</t>
+          <t>133,2 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.819 m</t>
+          <t>1.907 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>126,1 km</t>
+          <t>131,7 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.063 m</t>
+          <t>1.819 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>122,2 km</t>
+          <t>126,1 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.463 m</t>
+          <t>1.063 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A340"/>
+  <dimension ref="A1:A354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,2373 +946,2471 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5014.8_2009_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>12008.4_3832_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>401.2_179_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>48019.1_21921_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>12003.8_4287_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>16520.2_4844_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10027.3_2906_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>5022.6_1526_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>3179.5_1064_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>9027.2_3128_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>6137.8_2406_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>4899.6_1578_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>5122.9_1812_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>684,6 km</t>
+          <t>687,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.121 m</t>
+          <t>9.152 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>481,7 km</t>
+          <t>491,7 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.411 m</t>
+          <t>6.543 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>474,4 km</t>
+          <t>486,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.064 m</t>
+          <t>4.160 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>333,0 km</t>
+          <t>346,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.745 m</t>
+          <t>3.896 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>296,3 km</t>
+          <t>304,6 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.514 m</t>
+          <t>3.621 m</t>
         </is>
       </c>
     </row>
@@ -573,46 +573,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>226,0 km</t>
+          <t>234,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.402 m</t>
+          <t>2.504 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>219,8 km</t>
+          <t>230,7 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.825 m</t>
+          <t>1.882 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>215,6 km</t>
+          <t>222,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.758 m</t>
+          <t>1.825 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>202,5 km</t>
+          <t>217,5 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.572 m</t>
+          <t>1.704 m</t>
         </is>
       </c>
     </row>
@@ -641,63 +641,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>194,7 km</t>
+          <t>202,8 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.848 m</t>
+          <t>1.921 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>192,8 km</t>
+          <t>201,6 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.481 m</t>
+          <t>2.893 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>191,6 km</t>
+          <t>194,5 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.761 m</t>
+          <t>2.640 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>184,5 km</t>
+          <t>192,8 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.510 m</t>
+          <t>2.481 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A354"/>
+  <dimension ref="A1:A366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,1687 +946,1687 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
@@ -2640,777 +2640,861 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>4540.8_1823_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>15200.8_10718_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>7025.4_3008_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>10533.4_4020_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>10001.9_4466_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>12004.8_4293_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>18102.7_4949_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>8024.4_2933_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>6549.3_2336_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>15504.3_3950_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>4759.9_1521_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>12003.8_4287_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>687,9 km</t>
+          <t>731,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.152 m</t>
+          <t>10.097 m</t>
         </is>
       </c>
     </row>
@@ -483,34 +483,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>491,7 km</t>
+          <t>499,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.543 m</t>
+          <t>4.267 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>486,9 km</t>
+          <t>493,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.160 m</t>
+          <t>6.551 m</t>
         </is>
       </c>
     </row>
@@ -556,46 +556,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>243,1 km</t>
+          <t>250,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.946 m</t>
+          <t>2.076 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>234,0 km</t>
+          <t>236,7 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.504 m</t>
+          <t>1.935 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230,7 km</t>
+          <t>234,0 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.882 m</t>
+          <t>2.504 m</t>
         </is>
       </c>
     </row>
@@ -641,80 +641,80 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>202,8 km</t>
+          <t>211,2 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.921 m</t>
+          <t>1.986 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>201,6 km</t>
+          <t>203,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.893 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>194,5 km</t>
+          <t>201,6 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.640 m</t>
+          <t>2.893 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>192,8 km</t>
+          <t>201,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.481 m</t>
+          <t>2.732 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>182,1 km</t>
+          <t>192,8 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.104 m</t>
+          <t>2.481 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>173,7 km</t>
+          <t>178,5 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.226 m</t>
+          <t>2.276 m</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>126,1 km</t>
+          <t>129,2 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>94,2 km</t>
+          <t>101,3 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>711 m</t>
+          <t>776 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A366"/>
+  <dimension ref="A1:A378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,917 +946,917 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
@@ -1870,1631 +1870,1715 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4638.4_1469_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>8069.5_2626_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1688.8_1103_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>11016.5_4519_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>9683.4_3490_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>4814.5_1705_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>13460.9_4967_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>5014.5_1626_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2172.3_1042_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>12326.4_4833_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>48019.1_21921_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2014.2_647_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>499,5 km</t>
+          <t>504,2 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.267 m</t>
+          <t>4.303 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>346,0 km</t>
+          <t>372,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.896 m</t>
+          <t>4.190 m</t>
         </is>
       </c>
     </row>
@@ -551,136 +551,136 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250,8 km</t>
+          <t>259,3 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.076 m</t>
+          <t>2.766 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>236,7 km</t>
+          <t>250,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.935 m</t>
+          <t>2.076 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>234,0 km</t>
+          <t>236,7 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.504 m</t>
+          <t>1.935 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>222,8 km</t>
+          <t>230,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.825 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>217,5 km</t>
+          <t>222,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.704 m</t>
+          <t>1.825 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>211,2 km</t>
+          <t>218,6 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.986 m</t>
+          <t>3.072 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>203,2 km</t>
+          <t>211,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.199 m</t>
+          <t>1.986 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>201,6 km</t>
+          <t>203,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.893 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>168,1 km</t>
+          <t>174,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.045 m</t>
+          <t>2.109 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>133,2 km</t>
+          <t>150,2 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.907 m</t>
+          <t>2.078 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A378"/>
+  <dimension ref="A1:A385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,1946 +946,1946 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
@@ -2899,49 +2899,49 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
@@ -2955,630 +2955,679 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5307.6_1655_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>5064.3_1832_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>4339.7_1200_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1002.0_533_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>15013.7_5517_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2185.4_792_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>5122.9_1812_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>731,9 km</t>
+          <t>743,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.097 m</t>
+          <t>10.243 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>643,0 km</t>
+          <t>665,0 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.084 m</t>
+          <t>10.322 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>493,1 km</t>
+          <t>498,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.551 m</t>
+          <t>6.613 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>372,0 km</t>
+          <t>377,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.190 m</t>
+          <t>4.253 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>304,6 km</t>
+          <t>325,8 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.621 m</t>
+          <t>3.849 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>259,3 km</t>
+          <t>264,2 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.766 m</t>
+          <t>2.823 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250,8 km</t>
+          <t>262,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.076 m</t>
+          <t>2.172 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>236,7 km</t>
+          <t>242,4 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.935 m</t>
+          <t>1.971 m</t>
         </is>
       </c>
     </row>
@@ -619,68 +619,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>222,8 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.825 m</t>
+          <t>2.093 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>218,6 km</t>
+          <t>222,8 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.072 m</t>
+          <t>1.825 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>211,2 km</t>
+          <t>218,6 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.986 m</t>
+          <t>3.072 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>203,2 km</t>
+          <t>214,8 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.199 m</t>
+          <t>2.722 m</t>
         </is>
       </c>
     </row>
@@ -692,29 +692,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>201,0 km</t>
+          <t>205,9 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.732 m</t>
+          <t>2.787 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>192,8 km</t>
+          <t>203,2 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.481 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>178,9 km</t>
+          <t>189,2 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.199 m</t>
+          <t>1.281 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>178,5 km</t>
+          <t>183,5 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.276 m</t>
+          <t>2.336 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>152,0 km</t>
+          <t>171,6 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.026 m</t>
+          <t>2.249 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150,5 km</t>
+          <t>162,0 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.028 m</t>
+          <t>1.119 m</t>
         </is>
       </c>
     </row>
@@ -811,46 +811,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>150,2 km</t>
+          <t>155,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.078 m</t>
+          <t>2.139 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rian  S.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>131,7 km</t>
+          <t>141,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.819 m</t>
+          <t>1.208 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Rian  S.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>129,2 km</t>
+          <t>131,7 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.063 m</t>
+          <t>1.819 m</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>101,3 km</t>
+          <t>106,2 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>776 m</t>
+          <t>833 m</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>92,8 km</t>
+          <t>102,8 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>936 m</t>
+          <t>978 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A385"/>
+  <dimension ref="A1:A406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,2688 +946,2835 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>8529.2_2334_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>4937.4_1783_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>3012.4_1258_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>6014.2_1803_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>5010.6_1464_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>5006.8_1080_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>10025.6_4018_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>5894.5_1785_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>4214.8_2018_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>6604.5_1998_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>3179.5_1064_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>10004.1_2868_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>6014.8_2936_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>15057.9_8625_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1004.8_315_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>10120.4_4000_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>7007.7_5703_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>21470.9_7911_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>469.2_158_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>10022.8_3774_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>25257.1_8319_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -483,34 +483,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lindelmo A.</t>
+          <t>Mecinho Tôrres M.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>504,2 km</t>
+          <t>505,4 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.303 m</t>
+          <t>6.716 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mecinho Tôrres M.</t>
+          <t>Lindelmo A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>498,1 km</t>
+          <t>504,2 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.613 m</t>
+          <t>4.303 m</t>
         </is>
       </c>
     </row>
@@ -551,34 +551,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>264,2 km</t>
+          <t>270,0 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.823 m</t>
+          <t>2.217 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>262,8 km</t>
+          <t>264,2 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.172 m</t>
+          <t>2.823 m</t>
         </is>
       </c>
     </row>
@@ -687,68 +687,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>205,9 km</t>
+          <t>208,4 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.787 m</t>
+          <t>1.226 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>203,2 km</t>
+          <t>205,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.199 m</t>
+          <t>2.787 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>189,2 km</t>
+          <t>192,5 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.281 m</t>
+          <t>2.450 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>183,5 km</t>
+          <t>189,2 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.336 m</t>
+          <t>1.281 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>174,1 km</t>
+          <t>184,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.109 m</t>
+          <t>2.232 m</t>
         </is>
       </c>
     </row>
@@ -789,34 +789,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>162,0 km</t>
+          <t>164,3 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.119 m</t>
+          <t>2.248 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>155,1 km</t>
+          <t>162,0 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.139 m</t>
+          <t>1.119 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A406"/>
+  <dimension ref="A1:A413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,322 +946,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
@@ -1275,245 +1275,245 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
@@ -1527,749 +1527,749 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
@@ -2283,994 +2283,994 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
@@ -3284,476 +3284,476 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
@@ -3767,14 +3767,63 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>6025.8_2464_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>5079.1_1762_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>6023.8_2112_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>5888.2_1831_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>10008.1_2966_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>7516.9_3203_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>3138.1_1120_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>743,0 km</t>
+          <t>758,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.243 m</t>
+          <t>10.385 m</t>
         </is>
       </c>
     </row>
@@ -539,46 +539,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>325,8 km</t>
+          <t>333,9 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.849 m</t>
+          <t>3.952 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>270,0 km</t>
+          <t>272,2 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.217 m</t>
+          <t>2.928 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>264,2 km</t>
+          <t>270,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.823 m</t>
+          <t>2.217 m</t>
         </is>
       </c>
     </row>
@@ -590,80 +590,80 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>242,4 km</t>
+          <t>253,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.971 m</t>
+          <t>2.060 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>230,8 km</t>
+          <t>231,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.822 m</t>
+          <t>1.948 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>224,2 km</t>
+          <t>230,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.093 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>222,8 km</t>
+          <t>226,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.825 m</t>
+          <t>3.152 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>218,6 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.072 m</t>
+          <t>2.093 m</t>
         </is>
       </c>
     </row>
@@ -687,34 +687,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>208,4 km</t>
+          <t>213,9 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.226 m</t>
+          <t>2.890 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>205,9 km</t>
+          <t>208,4 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.787 m</t>
+          <t>1.226 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>192,5 km</t>
+          <t>200,4 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.450 m</t>
+          <t>2.552 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>189,2 km</t>
+          <t>195,2 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.281 m</t>
+          <t>1.360 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>184,1 km</t>
+          <t>194,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.232 m</t>
+          <t>2.351 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>171,6 km</t>
+          <t>179,6 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.249 m</t>
+          <t>2.371 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>164,3 km</t>
+          <t>170,3 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.248 m</t>
+          <t>2.302 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>162,0 km</t>
+          <t>168,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.119 m</t>
+          <t>1.130 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>141,2 km</t>
+          <t>149,4 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.208 m</t>
+          <t>1.218 m</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>131,7 km</t>
+          <t>139,9 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.819 m</t>
+          <t>1.925 m</t>
         </is>
       </c>
     </row>
@@ -908,15 +908,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Denis G.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>68,5 km</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>581 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Pablo T.</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>59,2 km</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>870 m</t>
         </is>
@@ -933,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A413"/>
+  <dimension ref="A1:A435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,1603 +963,1603 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
@@ -2556,1274 +2573,1428 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>6046.5_3239_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>4613.1_1806_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>10120.4_4000_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>10106.6_2889_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>15504.3_3950_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>7025.4_3008_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>5219.5_2096_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>469.2_158_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>6773.6_1852_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>6607.1_1718_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>7007.7_5703_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>401.2_179_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2172.3_1042_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>13047.0_4460_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>5014.3_1731_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>8009.5_2499_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>5064.3_1832_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>9027.6_3019_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>12641.8_3977_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>6053.8_2077_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>3006.0_910_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2014.2_647_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -539,46 +539,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>333,9 km</t>
+          <t>339,9 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.952 m</t>
+          <t>4.008 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fabio O.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>272,2 km</t>
+          <t>275,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.928 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Fabio O.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>270,0 km</t>
+          <t>272,2 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.217 m</t>
+          <t>2.928 m</t>
         </is>
       </c>
     </row>
@@ -602,68 +602,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>231,3 km</t>
+          <t>235,2 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.948 m</t>
+          <t>2.150 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230,8 km</t>
+          <t>232,9 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.822 m</t>
+          <t>3.210 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>226,9 km</t>
+          <t>231,3 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.152 m</t>
+          <t>1.948 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>224,2 km</t>
+          <t>230,8 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.093 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
@@ -721,51 +721,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200,4 km</t>
+          <t>204,1 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.552 m</t>
+          <t>2.430 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>195,2 km</t>
+          <t>200,4 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.360 m</t>
+          <t>2.552 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>194,1 km</t>
+          <t>195,2 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.351 m</t>
+          <t>1.360 m</t>
         </is>
       </c>
     </row>
@@ -857,34 +857,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>106,2 km</t>
+          <t>108,5 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>833 m</t>
+          <t>1.045 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>102,8 km</t>
+          <t>106,2 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>978 m</t>
+          <t>833 m</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>70,5 km</t>
+          <t>74,6 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>646 m</t>
+          <t>695 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A435"/>
+  <dimension ref="A1:A443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,490 +963,490 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
@@ -1460,2009 +1460,2009 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
@@ -3476,525 +3476,581 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>55771.9_25830_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>8013.1_2082_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2880.9_1210_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>6518.4_2914_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>8040.3_2607_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>7510.8_2318_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>12641.8_3977_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>5027.8_1361_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>758,0 km</t>
+          <t>763,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.385 m</t>
+          <t>10.446 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>505,4 km</t>
+          <t>514,4 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.716 m</t>
+          <t>6.826 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>377,0 km</t>
+          <t>390,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.253 m</t>
+          <t>4.351 m</t>
         </is>
       </c>
     </row>
@@ -590,63 +590,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>253,5 km</t>
+          <t>263,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.060 m</t>
+          <t>2.141 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>235,2 km</t>
+          <t>248,9 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.150 m</t>
+          <t>3.402 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>232,9 km</t>
+          <t>236,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.210 m</t>
+          <t>1.989 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>231,3 km</t>
+          <t>235,2 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.948 m</t>
+          <t>2.150 m</t>
         </is>
       </c>
     </row>
@@ -670,68 +670,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>214,8 km</t>
+          <t>224,4 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.722 m</t>
+          <t>3.027 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>213,9 km</t>
+          <t>223,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.890 m</t>
+          <t>2.833 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>208,4 km</t>
+          <t>214,1 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.226 m</t>
+          <t>2.538 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>204,1 km</t>
+          <t>208,4 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.430 m</t>
+          <t>1.226 m</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>195,2 km</t>
+          <t>197,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>170,3 km</t>
+          <t>174,5 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.302 m</t>
+          <t>2.366 m</t>
         </is>
       </c>
     </row>
@@ -857,34 +857,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>108,5 km</t>
+          <t>111,2 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.045 m</t>
+          <t>863 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>106,2 km</t>
+          <t>108,5 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>833 m</t>
+          <t>1.045 m</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>68,5 km</t>
+          <t>73,6 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>581 m</t>
+          <t>608 m</t>
         </is>
       </c>
     </row>
@@ -936,6 +936,23 @@
       <c r="C30" t="inlineStr">
         <is>
           <t>870 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Alan P.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>58,1 km</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>594 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A443"/>
+  <dimension ref="A1:A463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,3094 +980,3234 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>4204.6_2091_🔋.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>10027.6_2938_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>10024.3_3157_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10032.4_4120_B.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10017.6_3398_B.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>2436.6_730_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>10026.5_2992_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>16026.2_5253_Q.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4094.1_1423_W.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10035.4_3536_(.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>3058.2_1279_L.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>8724.4_2500_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>8534.7_3164_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>10106.6_2889_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>25257.1_8319_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>55771.9_25830_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>47036.4_21887_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>15013.7_5517_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>10027.0_4492_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>7061.6_2110_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>5833.1_1807_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>7007.7_5703_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>5015.8_1609_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>6025.8_2464_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>4840.9_1332_Q.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>12587.9_4015_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>4153.2_3559_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>5533.2_1998_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>18012.2_5886_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>5012.3_2098_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>5014.5_1626_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>275,8 km</t>
+          <t>288,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>2.376 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>263,5 km</t>
+          <t>268,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.141 m</t>
+          <t>2.190 m</t>
         </is>
       </c>
     </row>
@@ -607,46 +607,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>248,9 km</t>
+          <t>254,9 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.402 m</t>
+          <t>3.455 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>236,8 km</t>
+          <t>242,2 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.989 m</t>
+          <t>2.219 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>235,2 km</t>
+          <t>236,8 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.150 m</t>
+          <t>1.989 m</t>
         </is>
       </c>
     </row>
@@ -738,34 +738,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jose S.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200,4 km</t>
+          <t>200,7 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.552 m</t>
+          <t>1.367 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Jose S.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>197,1 km</t>
+          <t>200,4 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.360 m</t>
+          <t>2.552 m</t>
         </is>
       </c>
     </row>
@@ -789,34 +789,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>174,5 km</t>
+          <t>175,3 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.366 m</t>
+          <t>1.130 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>168,1 km</t>
+          <t>174,5 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.130 m</t>
+          <t>2.366 m</t>
         </is>
       </c>
     </row>
@@ -891,34 +891,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bruninho W.</t>
+          <t>Denis G.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>74,6 km</t>
+          <t>83,6 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>695 m</t>
+          <t>690 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Denis G.</t>
+          <t>Bruninho W.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>73,6 km</t>
+          <t>74,6 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>608 m</t>
+          <t>695 m</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A463"/>
+  <dimension ref="A1:A474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,3066 +980,3066 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>3058.2_1279_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4204.6_2091_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>6030.6_2410_Q.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5005.9_1750_B.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>2436.6_730_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4094.1_1423_W.</t>
+          <t>10017.6_3398_B.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>10035.4_3536_(.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>13021.6_4057_F.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10027.6_2938_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10032.4_4120_B.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10023.7_3190_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>10024.3_3157_P.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>5005.5_1972_(.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>16026.2_5253_Q.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>10017.6_3398_B.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2436.6_730_L.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10026.5_2992_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>18012.2_5886_P.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>16026.2_5253_Q.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3.5_6_S.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>10027.6_2938_P.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10035.4_3536_(.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10515.1_3255_W.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4204.6_2091_🔋.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>10024.3_3157_P.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10026.5_2992_P.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
@@ -4053,161 +4053,238 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>3058.2_1279_L.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>18012.2_5886_P.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>4778.0_1349_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>10013.4_3721_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>4891.7_1690_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2172.3_1042_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>5021.9_1788_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>5533.2_1998_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>9027.2_3128_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>7801.9_2997_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>15057.9_8625_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>7012.6_2365_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>10305.8_2846_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>763,0 km</t>
+          <t>806,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.446 m</t>
+          <t>10.848 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>390,0 km</t>
+          <t>418,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.351 m</t>
+          <t>4.582 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>272,2 km</t>
+          <t>282,3 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.928 m</t>
+          <t>3.042 m</t>
         </is>
       </c>
     </row>
@@ -602,51 +602,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>254,9 km</t>
+          <t>255,5 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.455 m</t>
+          <t>2.127 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>242,2 km</t>
+          <t>254,9 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.219 m</t>
+          <t>3.455 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>236,8 km</t>
+          <t>242,2 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.989 m</t>
+          <t>2.219 m</t>
         </is>
       </c>
     </row>
@@ -670,68 +670,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>224,4 km</t>
+          <t>225,9 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.027 m</t>
+          <t>1.306 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>223,5 km</t>
+          <t>224,4 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.833 m</t>
+          <t>3.027 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>214,1 km</t>
+          <t>223,5 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.538 m</t>
+          <t>2.833 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>208,4 km</t>
+          <t>214,1 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.226 m</t>
+          <t>2.538 m</t>
         </is>
       </c>
     </row>
@@ -857,34 +857,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Lucas S.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>111,2 km</t>
+          <t>121,5 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>863 m</t>
+          <t>1.184 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucas S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>108,5 km</t>
+          <t>121,2 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.045 m</t>
+          <t>963 m</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A474"/>
+  <dimension ref="A1:A482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,252 +980,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>10017.6_3398_B.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4094.1_1423_W.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10032.4_4120_B.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3058.2_1279_L.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
@@ -1239,3052 +1239,3108 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6030.6_2410_Q.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3.5_6_S.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2436.6_730_L.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10017.6_3398_B.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10035.4_3536_(.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>18012.2_5886_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>9553.3_3428_L.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>9150.8_3471_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>10027.6_2938_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10035.4_3536_(.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5005.5_1972_(.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>16026.2_5253_Q.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5005.9_1750_B.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>10050.1_3089_O.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2436.6_730_L.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>18012.2_5886_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>28006.9_9805_F.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>43016.0_17265_B.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>10024.3_3157_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10027.6_2938_P.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>3058.2_1279_L.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6030.6_2410_Q.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>10515.1_3255_W.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4204.6_2091_🔋.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>10024.3_3157_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>13021.6_4057_F.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>10023.7_3190_P.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>4204.6_2091_🔋.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>13029.4_4879_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>10026.5_2992_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>5005.5_1972_(.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>16026.2_5253_Q.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>10026.5_2992_P.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>17540.5_5163_R.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5005.8_1649_H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>12006.9_5463_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>401.2_179_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>15013.7_5517_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>16520.2_4844_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>11097.5_3842_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>10031.8_2663_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>5005.4_2618_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>806,0 km</t>
+          <t>810,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.848 m</t>
+          <t>10.917 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>665,0 km</t>
+          <t>675,0 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.322 m</t>
+          <t>10.342 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>514,4 km</t>
+          <t>525,4 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.826 m</t>
+          <t>6.976 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>418,0 km</t>
+          <t>428,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.582 m</t>
+          <t>4.600 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>339,9 km</t>
+          <t>349,9 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.008 m</t>
+          <t>4.094 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>288,8 km</t>
+          <t>306,0 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.376 m</t>
+          <t>2.533 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>282,3 km</t>
+          <t>294,3 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.042 m</t>
+          <t>3.174 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>268,5 km</t>
+          <t>278,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.190 m</t>
+          <t>2.209 m</t>
         </is>
       </c>
     </row>
@@ -619,68 +619,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>254,9 km</t>
+          <t>255,2 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.455 m</t>
+          <t>2.349 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>242,2 km</t>
+          <t>254,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.219 m</t>
+          <t>3.455 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Luiz Fernando Rafael De Arruda R.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230,8 km</t>
+          <t>238,1 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.822 m</t>
+          <t>1.332 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luiz Fernando Rafael De Arruda R.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>225,9 km</t>
+          <t>230,8 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.306 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
@@ -704,34 +704,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>223,5 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.833 m</t>
+          <t>2.554 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>214,1 km</t>
+          <t>223,5 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.538 m</t>
+          <t>2.833 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200,7 km</t>
+          <t>215,7 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.367 m</t>
+          <t>1.494 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>179,6 km</t>
+          <t>190,3 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.371 m</t>
+          <t>1.238 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>175,3 km</t>
+          <t>183,9 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.130 m</t>
+          <t>2.435 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>174,5 km</t>
+          <t>179,5 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.366 m</t>
+          <t>2.385 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>149,4 km</t>
+          <t>159,5 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.218 m</t>
+          <t>1.238 m</t>
         </is>
       </c>
     </row>
@@ -896,63 +896,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>83,6 km</t>
+          <t>93,8 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>690 m</t>
+          <t>710 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bruninho W.</t>
+          <t>Alan P.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>74,6 km</t>
+          <t>76,1 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>695 m</t>
+          <t>771 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pablo T.</t>
+          <t>Bruninho W.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>59,2 km</t>
+          <t>74,6 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>870 m</t>
+          <t>695 m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alan P.</t>
+          <t>Pablo T.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>58,1 km</t>
+          <t>59,2 km</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>594 m</t>
+          <t>870 m</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A482"/>
+  <dimension ref="A1:A503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,3367 +980,3514 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10017.6_3398_B.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3.5_6_S.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>13029.4_4879_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>3058.2_1279_L.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>16026.2_5253_Q.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>9150.8_3471_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10026.5_2992_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10023.7_3190_P.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>18012.2_5886_P.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>10095.1_3241_B.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10515.1_3255_W.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9553.3_3428_L.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9150.8_3471_L.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>10027.6_2938_P.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>10028.1_3479_(.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>9553.3_3428_L.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>10035.4_3536_(.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>4940.1_1533_B.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>10017.6_3398_B.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>10050.1_3089_O.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>5006.9_2178_🔋.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2436.6_730_L.</t>
+          <t>6030.6_2410_Q.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>12014.2_3864_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>10035.4_3536_(.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>18012.2_5886_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>28006.9_9805_F.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>43016.0_17265_B.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10024.3_3157_P.</t>
+          <t>3004.8_898_L.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>10050.1_3089_O.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>28006.9_9805_F.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3058.2_1279_L.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>2436.6_730_L.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>10048.6_3686_F.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5005.9_1750_B.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>18033.5_6309_P.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6030.6_2410_Q.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>12018.5_3975_O.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>10024.3_3157_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4204.6_2091_🔋.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>13029.4_4879_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>10027.6_2938_P.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>7032.6_1900_L.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>17540.5_5163_R.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>5005.5_1972_(.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>16026.2_5253_Q.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>13021.6_4057_F.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>10026.5_2992_P.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>4094.1_1423_W.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>17540.5_5163_R.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>10015.5_3108_O.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>43016.0_17265_B.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>10032.4_4120_B.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>10001.9_4466_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2003.1_722_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>9562.8_3145_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>5695.9_2465_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>515.9_237_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>4932.1_1432_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>9902.7_3162_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2761.5_1068_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>5010.3_1888_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>8200.5_2738_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>8025.0_2507_W.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>8024.4_2933_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>4204.6_2091_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>12470.8_3701_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>56121.5_25636_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>12151.4_3791_R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>3059.2_956_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>5014.3_1731_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>10022.1_2875_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>1885.0_952_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>5005.5_1972_(.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>349,9 km</t>
+          <t>364,9 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.094 m</t>
+          <t>4.278 m</t>
         </is>
       </c>
     </row>
@@ -602,51 +602,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eduarda L.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>255,5 km</t>
+          <t>269,9 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.127 m</t>
+          <t>3.641 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Eduarda L.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>255,2 km</t>
+          <t>255,5 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.349 m</t>
+          <t>2.127 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>254,9 km</t>
+          <t>255,2 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.455 m</t>
+          <t>2.349 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200,4 km</t>
+          <t>204,7 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.552 m</t>
+          <t>2.617 m</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>121,5 km</t>
+          <t>129,5 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.184 m</t>
+          <t>1.285 m</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>121,2 km</t>
+          <t>126,2 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>963 m</t>
+          <t>998 m</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A503"/>
+  <dimension ref="A1:A510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,945 +980,945 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>4932.1_1432_W.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>10016.3_3304_W.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15005.1_6183_H.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>6531.3_2563_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10004.1_2868_L.</t>
+          <t>9902.7_3162_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5023.2_1813_Q.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4778.0_1349_B.</t>
+          <t>17014.8_5635_Q.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9048.4_3554_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10042.8_3601_(.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8529.2_2334_L.</t>
+          <t>5737.7_1721_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>44008.8_21351_B.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1139.2_971_R.</t>
+          <t>9553.3_3428_L.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6023.1_2321_B.</t>
+          <t>5105.7_1768_B.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>12014.8_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13029.4_4879_S.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>5007.0_1820_H.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1734.2_553_B.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9683.4_3490_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>7061.6_2110_B.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10023.9_3586_(.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>2971.2_2253_R.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>13344.7_5916_H.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>15009.6_4778_L.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3058.2_1279_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>6773.6_1852_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5017.9_2549_W.</t>
+          <t>8008.6_2696_🔋.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10071.3_3601_B.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>11.3_16_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>18012.2_5886_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7511.5_2322_F.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>8028.3_3060_T.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5017.3_1786_B.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>2436.6_730_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9984.2_3010_S.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5122.9_1812_W.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16026.2_5253_Q.</t>
+          <t>5245.9_1540_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10261.8_3736_(.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>10120.4_4000_H.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9150.8_3471_L.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7008.0_2227_A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11145.2_4223_B.</t>
+          <t>5760.0_2094_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10026.5_2992_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6051.3_1877_O.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6607.1_1718_L.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>4919.0_1639_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>1057.3_319_R.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7041.9_2342_O.</t>
+          <t>9027.6_3019_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3179.5_1064_R.</t>
+          <t>5009.5_1305_Q.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5003.8_1701_H.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>22012.0_8790_F.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5014.5_1626_W.</t>
+          <t>2003.1_722_B.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21092.9_7727_R.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4073.8_1409_B.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4933.2_1199_L.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6009.3_2290_B.</t>
+          <t>28006.9_9805_F.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>15010.8_6619_H.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12016.2_3683_F.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>6023.8_2112_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10095.1_3241_B.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>3058.2_1279_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8069.5_2626_O.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20017.1_6874_F.</t>
+          <t>5024.1_1795_(.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>53121.7_36050_B.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>7230.5_2794_B.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>10022.8_3774_H.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6146.9_2154_B.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4678.6_1635_A.</t>
+          <t>10013.5_3516_W.</t>
         </is>
       </c>
     </row>
@@ -1932,546 +1932,546 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>55771.9_25830_B.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7859.6_2735_S.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5011.3_1521_A.</t>
+          <t>21306.6_7154_Q.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>1174.8_175_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10006.2_2869_L.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>21169.7_7158_O.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>13011.5_4096_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>2172.3_1042_R.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10028.1_3479_(.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6014.2_1803_Q.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7204.3_2052_Q.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>13460.9_4967_L.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7510.8_2318_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>13021.6_4057_F.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9553.3_3428_L.</t>
+          <t>8316.3_2473_Q.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5175.0_1718_R.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3006.0_910_L.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>6006.6_1749_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>8102.6_2153_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>8506.9_2757_O.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>11096.8_3802_(.</t>
+          <t>1004.2_324_R.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>3013.0_846_B.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5012.3_2098_H.</t>
+          <t>26016.8_8701_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5513.4_1789_Q.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8198.4_2307_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6510.7_2169_W.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>7032.6_1900_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>7083.1_2912_H.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>11004.8_3370_A.</t>
+          <t>5537.2_1928_B.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>15012.8_4809_Q.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>10023.7_3190_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5307.6_1655_W.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>10027.6_2938_P.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>7011.4_2074_W.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4992.7_1755_R.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>5008.8_1593_(.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5833.1_1807_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4940.1_1533_B.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>4840.9_1332_Q.</t>
+          <t>10031.3_3296_B.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4638.4_1469_W.</t>
+          <t>11018.2_3436_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>10013.4_3721_H.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>5736.9_1901_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10026.5_2992_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>6025.8_2464_(.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>10574.5_3252_R.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10013.7_3336_B.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6037.7_1777_L.</t>
+          <t>10100.9_3336_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10017.6_3398_B.</t>
+          <t>4339.7_1200_🔋.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>12470.8_3701_A.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
@@ -2485,2009 +2485,2058 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>8025.0_2507_W.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>12012.0_4359_B.</t>
+          <t>10035.4_3536_(.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3.5_6_S.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>6030.6_2410_Q.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4899.6_1578_S.</t>
+          <t>11004.9_3283_A.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10305.8_2846_L.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5006.9_2178_🔋.</t>
+          <t>3290.3_1151_B.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>5005.8_1649_H.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>6030.6_2410_Q.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5219.5_2096_R.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>15009.9_5893_B.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>4750.1_1404_F.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>469.2_158_R.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>10408.0_3221_R.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8310.3_2295_L.</t>
+          <t>2095.2_1636_R.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>12014.2_3864_F.</t>
+          <t>24017.4_8697_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>10035.4_3536_(.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1004.8_315_R.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>11097.5_3842_O.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>18012.2_5886_P.</t>
+          <t>17007.2_5700_🔋.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>21470.9_7911_F.</t>
+          <t>6604.5_1998_L.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4912.8_1286_🔋.</t>
+          <t>4943.8_1258_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>6508.6_2257_W.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>15100.7_5557_(.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>444.7_139_W.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>3014.7_822_B.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5244.3_1810_L.</t>
+          <t>5894.5_1785_T.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>3096.7_4568_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8269.0_2920_S.</t>
+          <t>12003.8_4287_Q.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>10031.0_2997_O.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>3006.0_910_L.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5024.7_1492_F.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>10355.4_3680_B.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>11005.6_3252_A.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>10362.8_6733_🔋.</t>
+          <t>11145.2_4223_B.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3004.8_898_L.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10780.1_3270_A.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>4887.3_1332_W.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>43016.0_17265_B.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5013.4_1650_(.</t>
+          <t>10408.0_3221_R.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>12022.4_3842_F.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>5017.3_1786_B.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10515.1_3255_W.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8364.0_2984_L.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6100.0_2246_L.</t>
+          <t>6037.7_1777_L.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>15336.7_5958_B.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>4887.3_1332_W.</t>
+          <t>10048.6_3686_F.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5014.8_1403_W.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5012.3_2098_H.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>6023.1_2321_B.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10050.1_3089_O.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5030.5_1643_B.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>16026.2_5253_Q.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5005.9_1750_B.</t>
+          <t>12018.5_3975_O.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10009.3_2896_A.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>10016.7_3069_W.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5005.5_1972_(.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>28006.9_9805_F.</t>
+          <t>9048.4_3554_S.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>4765.3_1809_T.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>3179.5_1064_R.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>10879.8_3328_A.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>12641.8_3977_A.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>11005.6_3252_A.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2436.6_730_L.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10048.6_3686_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10032.4_4120_B.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>18033.5_6309_P.</t>
+          <t>4912.8_1286_🔋.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>5030.5_1643_B.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>12018.5_3975_O.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6023.1_2082_B.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5023.2_1813_Q.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>7007.7_5703_🔋.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10879.8_3328_A.</t>
+          <t>12016.2_3683_F.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>10095.1_3241_B.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>6009.3_2290_B.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>6100.0_2246_L.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5026.3_1748_(.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2440.9_748_B.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>5003.8_1701_H.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>7012.6_2365_B.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10024.3_3157_P.</t>
+          <t>17540.5_5163_R.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>12151.4_3791_R.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>4987.7_1610_R.</t>
+          <t>18033.5_6309_P.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>5219.5_2096_R.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>9683.4_3490_S.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1020.7_482_R.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>10025.3_3506_S.</t>
+          <t>7012.6_2365_B.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>8009.5_2499_🔋.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>8534.7_3164_L.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>4204.6_2091_🔋.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>8364.0_2984_L.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>47.5_36_S.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>6623.0_2224_Q.</t>
+          <t>5244.3_1810_L.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5021.4_2461_H.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>4638.4_1469_W.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>20017.1_6874_F.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5888.2_1831_A.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>7801.9_2997_L.</t>
+          <t>6510.7_2169_W.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>10027.6_2938_P.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>11009.0_4656_B.</t>
+          <t>6609.8_2216_B.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>7032.6_1900_L.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>4940.1_1533_B.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>10027.0_4492_B.</t>
+          <t>10016.7_3069_W.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>3004.8_898_L.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>5507.6_1611_L.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>13029.4_4879_S.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5053.8_1563_R.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>17540.5_5163_R.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5006.9_2178_🔋.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>21634.6_6997_R.</t>
+          <t>10004.1_2868_L.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>15336.7_5958_B.</t>
+          <t>7511.5_2322_F.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4759.9_1521_S.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>25.3_30_L.</t>
+          <t>7.1_6_S.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>8040.2_2737_S.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>12022.4_3842_F.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6609.8_2216_B.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>4765.3_1809_T.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>8525.9_2945_Q.</t>
+          <t>3020.9_1081_B.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>5776.5_1760_A.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10006.2_2869_L.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5888.2_1831_A.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4821.0_1182_L.</t>
+          <t>11096.8_3802_(.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>10013.7_3336_B.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>15025.8_5254_B.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>842.2_770_R.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>10780.1_3270_A.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4933.2_1199_L.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>3020.9_1081_B.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>4780.8_1582_S.</t>
+          <t>5011.3_1521_A.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>11004.8_3370_A.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5175.0_1718_R.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>11016.5_4519_Q.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>4932.5_1501_O.</t>
+          <t>9150.8_3471_L.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>4094.1_1423_W.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>10015.5_3108_O.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>10031.0_2997_O.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>43016.0_17265_B.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>10050.1_3089_O.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6549.3_2336_S.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>5024.7_1492_F.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>7007.7_5703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>12004.8_4293_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>7801.9_2997_L.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>4778.0_1349_B.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>11097.5_3842_O.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>4821.0_1182_L.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>4204.6_2091_🔋.</t>
+          <t>10009.3_2896_A.</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>11016.5_4519_Q.</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>12151.4_3791_R.</t>
+          <t>6549.3_2336_S.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>44008.8_21351_B.</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5026.3_1748_(.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>25.3_30_L.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>5005.5_1972_(.</t>
+          <t>10028.1_3479_(.</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>10355.4_3680_B.</t>
+          <t>10017.6_3398_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>10015.5_3108_O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>4899.6_1578_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>12014.2_3864_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>6023.1_2082_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>4763.8_1720_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10024.3_3157_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_1000km_2026.xlsx
+++ b/Ranking_CNB_1000km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>675,0 km</t>
+          <t>684,1 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.342 m</t>
+          <t>10.473 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>525,4 km</t>
+          <t>548,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.976 m</t>
+          <t>7.272 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>364,9 km</t>
+          <t>373,4 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.278 m</t>
+          <t>4.406 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>306,0 km</t>
+          <t>313,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.533 m</t>
+          <t>2.570 m</t>
         </is>
       </c>
     </row>
@@ -585,34 +585,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wellington Silva. (.</t>
+          <t>Ismael Q.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>278,5 km</t>
+          <t>278,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.209 m</t>
+          <t>3.764 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ismael Q.</t>
+          <t>Wellington Silva. (.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>269,9 km</t>
+          <t>278,5 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.641 m</t>
+          <t>2.209 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>255,5 km</t>
+          <t>261,0 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.127 m</t>
+          <t>2.197 m</t>
         </is>
       </c>
     </row>
@@ -670,68 +670,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Denis H.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230,8 km</t>
+          <t>232,0 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.822 m</t>
+          <t>2.962 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>José Welligton Dos Santos W.</t>
+          <t>Denis H.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>224,4 km</t>
+          <t>230,8 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.027 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daniel B.</t>
+          <t>José Welligton Dos Santos W.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>224,2 km</t>
+          <t>224,4 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.554 m</t>
+          <t>3.027 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Daniel B.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>223,5 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.833 m</t>
+          <t>2.554 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>204,7 km</t>
+          <t>213,7 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.617 m</t>
+          <t>2.747 m</t>
         </is>
       </c>
     </row>
@@ -777,46 +777,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>190,3 km</t>
+          <t>195,3 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.238 m</t>
+          <t>1.281 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>183,9 km</t>
+          <t>185,5 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.435 m</t>
+          <t>2.460 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>179,5 km</t>
+          <t>183,9 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.385 m</t>
+          <t>2.435 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>159,5 km</t>
+          <t>163,7 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.238 m</t>
+          <t>1.240 m</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>76,1 km</t>
+          <t>79,1 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>771 m</t>
+          <t>778 m</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A510"/>
+  <dimension ref="A1:A523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,3563 +980,3654 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3029.5_1536_H.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9027.2_3128_B.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10023.7_3190_P.</t>
+          <t>5236.1_1583_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4932.1_1432_W.</t>
+          <t>48019.1_21921_B.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10016.3_3304_W.</t>
+          <t>5017.9_2549_W.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>8040.3_2607_O.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10025.6_4018_H.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5695.9_2465_(.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>13047.0_4460_W.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5209.6_1613_A.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6531.3_2563_B.</t>
+          <t>10027.0_4492_B.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5008.0_1650_(.</t>
+          <t>12004.8_4293_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9902.7_3162_A.</t>
+          <t>21470.9_7911_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5012.4_1845_H.</t>
+          <t>13011.5_4096_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>10025.3_3506_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>6014.2_1803_Q.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8223.8_2382_Q.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17014.8_5635_Q.</t>
+          <t>4204.6_2091_🔋.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10042.8_3601_(.</t>
+          <t>5012.7_1713_H.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>1139.2_971_R.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5737.7_1721_A.</t>
+          <t>4899.6_1578_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15013.7_5517_B.</t>
+          <t>4094.1_1423_W.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2014.2_647_B.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>12012.0_4359_B.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10023.7_3190_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>15005.1_6183_H.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9553.3_3428_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15010.1_5518_L.</t>
+          <t>5012.4_1845_H.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>8310.3_2295_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6645.9_2232_O.</t>
+          <t>10362.8_6733_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5105.7_1768_B.</t>
+          <t>4818.4_1469_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>6004.6_1614_🔋.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12014.8_3683_F.</t>
+          <t>1688.8_1103_R.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5007.0_1820_H.</t>
+          <t>1004.8_315_R.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>4940.1_1533_B.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5021.9_1788_(.</t>
+          <t>13021.6_4057_F.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7061.6_2110_B.</t>
+          <t>5022.6_1526_W.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8023.5_2686_O.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5010.8_2324_B.</t>
+          <t>5776.5_1760_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6006.7_1747_Q.</t>
+          <t>5021.9_1788_(.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21017.3_7815_(.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10023.9_3586_(.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>12012.3_4421_B.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2971.2_2253_R.</t>
+          <t>10021.6_3449_Q.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13344.7_5916_H.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15009.6_4778_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>4499.3_1358_T.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6773.6_1852_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>18012.2_5886_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8008.6_2696_🔋.</t>
+          <t>1002.5_1292_B.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25257.1_8319_O.</t>
+          <t>5021.4_2461_H.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4678.6_1635_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11.3_16_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6014.8_2936_B.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>8009.5_2499_🔋.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18012.2_5886_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4987.7_1610_R.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10305.8_2846_L.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4796.0_1315_O.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8028.3_3060_T.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5010.6_1464_B.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3029.5_1536_H.</t>
+          <t>4083.9_1625_A.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5005.9_1750_B.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4918.8_1487_S.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2436.6_730_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>25257.1_8319_O.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>15013.7_5517_B.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5245.9_1540_A.</t>
+          <t>9052.9_2955_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10261.8_3736_(.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10120.4_4000_H.</t>
+          <t>5006.9_2178_🔋.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7008.0_2227_A.</t>
+          <t>21634.6_6997_R.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5760.0_2094_L.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6607.1_1718_L.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5024.6_1753_(.</t>
+          <t>22012.0_8790_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10050.1_3089_O.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4919.0_1639_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057.3_319_R.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9027.6_3019_S.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5009.5_1305_Q.</t>
+          <t>2014.2_647_B.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>4247.7_1274_T.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>6006.7_1747_Q.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2003.1_722_B.</t>
+          <t>5053.8_1563_R.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21006.2_6306_L.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>15010.1_5518_L.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>21017.3_7815_(.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4073.8_1409_B.</t>
+          <t>10515.1_3255_W.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>11006.2_3422_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5236.1_1583_A.</t>
+          <t>6051.3_1877_O.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5015.8_1609_(.</t>
+          <t>15009.6_4778_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>28006.9_9805_F.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>21092.9_7727_R.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15010.8_6619_H.</t>
+          <t>7041.9_2342_O.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>9076.5_3626_L.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6023.8_2112_B.</t>
+          <t>1734.2_553_B.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5010.8_2324_B.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4818.4_1469_S.</t>
+          <t>9553.3_3428_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3058.2_1279_L.</t>
+          <t>11009.0_4656_🔋.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>4796.0_1315_O.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5022.6_1526_W.</t>
+          <t>7859.6_2735_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5024.1_1795_(.</t>
+          <t>18046.5_5264_L.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>12587.9_4015_A.</t>
+          <t>8069.5_2626_O.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>53121.7_36050_B.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7230.5_2794_B.</t>
+          <t>469.2_158_R.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5010.6_1464_B.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10022.8_3774_H.</t>
+          <t>5209.6_1613_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5695.9_2465_(.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>6623.0_2224_Q.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4083.9_1625_A.</t>
+          <t>4910.5_1712_R.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10013.5_3516_W.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6022.4_2122_F.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>55771.9_25830_B.</t>
+          <t>13460.9_4967_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>1002.0_533_R.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>15100.7_5557_(.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>13021.6_4057_F.</t>
+          <t>11006.2_3422_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5954.3_2852_🔋.</t>
+          <t>12587.9_4015_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21306.6_7154_Q.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8040.3_2607_O.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1174.8_175_S.</t>
+          <t>10105.5_3599_L.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>4702.3_1489_R.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>8300.3_2570_L.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5008.0_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>3011.2_1046_B.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2172.3_1042_R.</t>
+          <t>9984.2_3010_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5507.6_1611_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>4759.9_1521_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8040.2_2737_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10071.3_3601_B.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1002.5_1292_B.</t>
+          <t>10025.6_4018_H.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8316.3_2473_Q.</t>
+          <t>4918.8_1487_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6146.9_2154_B.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6006.6_1749_L.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8102.6_2153_L.</t>
+          <t>10028.1_3479_(.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>18046.5_5264_L.</t>
+          <t>5122.9_1812_W.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4840.9_1332_Q.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8506.9_2757_O.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1004.2_324_R.</t>
+          <t>4780.8_1582_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>12012.3_4421_B.</t>
+          <t>10024.3_3157_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3013.0_846_B.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>26016.8_8701_F.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5513.4_1789_Q.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8198.4_2307_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>7032.6_1900_L.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8023.5_2686_O.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8502.5_2418_L.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>7083.1_2912_H.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5537.2_1928_B.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15012.8_4809_Q.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6022.4_2122_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5013.4_1650_(.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10027.6_2938_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>8269.0_2920_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>842.2_770_R.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10105.5_3599_L.</t>
+          <t>5014.5_1626_W.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7011.4_2074_W.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>21200.0_6140_L.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8300.3_2570_L.</t>
+          <t>4992.7_1755_R.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6023.1_2082_B.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5008.8_1593_(.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5833.1_1807_A.</t>
+          <t>3096.7_4568_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10021.6_3449_Q.</t>
+          <t>5014.8_1403_W.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10031.3_3296_B.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>11018.2_3436_F.</t>
+          <t>10048.6_3686_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>6645.9_2232_O.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5736.9_1901_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4910.5_1712_R.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10026.5_2992_P.</t>
+          <t>9241.6_3253_🔋.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6025.8_2464_(.</t>
+          <t>5307.6_1655_W.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>10013.4_3721_H.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>3004.8_898_L.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10574.5_3252_R.</t>
+          <t>4932.5_1501_O.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10100.9_3336_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4339.7_1200_🔋.</t>
+          <t>7032.6_1900_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12470.8_3701_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>8952.2_3088_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>11009.0_4656_🔋.</t>
+          <t>8534.7_3164_L.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3716.0_1233_B.</t>
+          <t>5015.8_1609_(.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>28006.9_9805_F.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>7510.8_2318_F.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9076.5_3626_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8025.0_2507_W.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>10035.4_3536_(.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>21200.0_6140_L.</t>
+          <t>3716.0_1233_B.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6030.6_2410_Q.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>11004.9_3283_A.</t>
+          <t>5954.3_2852_🔋.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>15025.8_5254_B.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3290.3_1151_B.</t>
+          <t>12641.8_3977_A.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5005.8_1649_H.</t>
+          <t>21006.2_6306_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>47.5_36_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>2440.9_748_B.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>7204.3_2052_Q.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3011.2_1046_B.</t>
+          <t>10032.4_4120_B.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>15009.9_5893_B.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4750.1_1404_F.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5012.7_1713_H.</t>
+          <t>5024.6_1753_(.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>7.1_6_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>6014.8_2936_B.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>13047.0_4460_W.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4702.3_1489_R.</t>
+          <t>1020.7_482_R.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2095.2_1636_R.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>48019.1_21921_B.</t>
+          <t>8529.2_2334_L.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>24017.4_8697_F.</t>
+          <t>9150.8_3471_L.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>9027.2_3128_B.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1002.0_533_R.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>11009.0_4656_B.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1688.8_1103_R.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>17007.2_5700_🔋.</t>
+          <t>8223.8_2382_Q.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>6604.5_1998_L.</t>
+          <t>21169.7_7158_O.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4943.8_1258_S.</t>
+          <t>10095.1_3241_B.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>6508.6_2257_W.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4499.3_1358_T.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>444.7_139_W.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3014.7_822_B.</t>
+          <t>3.5_6_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5894.5_1785_T.</t>
+          <t>12018.5_3975_O.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3096.7_4568_S.</t>
+          <t>8525.9_2945_Q.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>12003.8_4287_Q.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>9241.6_3253_🔋.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
 